--- a/DRIVE/Orgãos funcionais/Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
+++ b/DRIVE/Orgãos funcionais/Operações/3.1 Projetos/Lista entregaveis projetos.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\2. Associados\3. Operações\3.1 Projetos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\castr\MINDSET\DRIVE\Orgãos funcionais\Operações\3.1 Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8827085-D3DD-4BCF-952E-4AA49287EFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511C5A47-359F-462C-8BD6-85FCBD9CFBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="📋 Registo" sheetId="2" r:id="rId1"/>
-    <sheet name="📦 Entregáveis" sheetId="3" r:id="rId2"/>
+    <sheet name="📦 Entregáveis" sheetId="3" r:id="rId1"/>
+    <sheet name="📋 Registo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <t>Nº</t>
   </si>
@@ -177,9 +177,6 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>POR-2025-0001PASS</t>
-  </si>
-  <si>
     <t>PA SoundSystem</t>
   </si>
   <si>
@@ -202,6 +199,27 @@
   </si>
   <si>
     <t>Espera do cliente</t>
+  </si>
+  <si>
+    <t>TIA</t>
+  </si>
+  <si>
+    <t>Visita obrigatoria</t>
+  </si>
+  <si>
+    <t>SAO-2026-0004-ESPL</t>
+  </si>
+  <si>
+    <t>POR-2025-0001-PASS</t>
+  </si>
+  <si>
+    <t>26004 (externo)</t>
+  </si>
+  <si>
+    <t>Zona exteriror (esplanada)</t>
+  </si>
+  <si>
+    <t>MARCAR</t>
   </si>
 </sst>
 </file>
@@ -996,6 +1014,715 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:N42"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="6" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+    </row>
+    <row r="2" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="L2" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="40"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="L3" s="26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="L4" s="27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="L5" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="10">
+        <f>COUNTA(C10:C19)</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="12">
+        <f>COUNTIF(G10:G59,"✅ Entregue")</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="14">
+        <f>COUNTIF(G10:G59,"⏳ Pendente")</f>
+        <v>1</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="16">
+        <f>COUNTIF(G10:G59,"🔄 Em revisão")</f>
+        <v>2</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="L7" s="23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="L8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+    </row>
+    <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="18">
+        <v>1</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="35">
+        <v>46161</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18">
+        <v>2</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="35">
+        <v>46147</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="18">
+        <v>3</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18">
+        <v>4</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="17"/>
+      <c r="B14" s="18">
+        <v>5</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="18">
+        <v>6</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18">
+        <v>7</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18">
+        <v>8</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="17"/>
+    </row>
+    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="17"/>
+      <c r="B18" s="18">
+        <v>9</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="17"/>
+    </row>
+    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="17"/>
+      <c r="B19" s="18">
+        <v>10</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18">
+        <v>11</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="17"/>
+    </row>
+    <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18">
+        <v>12</v>
+      </c>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="17"/>
+    </row>
+    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="17"/>
+      <c r="B22" s="18">
+        <v>13</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="17"/>
+    </row>
+    <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18">
+        <v>14</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="17"/>
+    </row>
+    <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="17"/>
+      <c r="B24" s="18">
+        <v>15</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="17"/>
+      <c r="B25" s="18">
+        <v>16</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="17"/>
+    </row>
+    <row r="26" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="17"/>
+      <c r="B26" s="18">
+        <v>17</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="17"/>
+      <c r="B27" s="18">
+        <v>18</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="17"/>
+      <c r="B28" s="18">
+        <v>19</v>
+      </c>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="17"/>
+    </row>
+    <row r="29" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17"/>
+      <c r="B29" s="18">
+        <v>20</v>
+      </c>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="17"/>
+    </row>
+    <row r="30" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="17"/>
+      <c r="B30" s="18">
+        <v>21</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="17"/>
+      <c r="B31" s="18">
+        <v>22</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="17"/>
+    </row>
+    <row r="32" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="17"/>
+      <c r="B32" s="18">
+        <v>23</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="17"/>
+    </row>
+    <row r="33" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="17"/>
+      <c r="B33" s="18">
+        <v>24</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="17"/>
+    </row>
+    <row r="34" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="17"/>
+      <c r="B34" s="18">
+        <v>25</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="17"/>
+    </row>
+    <row r="35" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="17"/>
+      <c r="B35" s="18">
+        <v>26</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="17"/>
+    </row>
+    <row r="36" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="17"/>
+      <c r="B36" s="18">
+        <v>27</v>
+      </c>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="17"/>
+    </row>
+    <row r="37" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="17"/>
+      <c r="B37" s="18">
+        <v>28</v>
+      </c>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="17"/>
+    </row>
+    <row r="38" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="17"/>
+      <c r="B38" s="18">
+        <v>29</v>
+      </c>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="17"/>
+    </row>
+    <row r="39" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="17"/>
+      <c r="B39" s="18">
+        <v>30</v>
+      </c>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="17"/>
+    </row>
+    <row r="41" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="36"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
+    </row>
+    <row r="42" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="B42:I42"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1153,14 +1880,26 @@
       <c r="A8" s="2"/>
       <c r="B8" s="3" t="str">
         <f t="shared" si="0"/>
-        <v>-0000-0000-</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+        <v>POR-2026-0004-ESPL</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>32</v>
+      </c>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
@@ -1268,699 +2007,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N42"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="6" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-    </row>
-    <row r="2" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="L2" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="L3" s="26" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="L4" s="27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="L5" s="19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="10">
-        <f>COUNTA(C10:C19)</f>
-        <v>3</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="12">
-        <f>COUNTIF(G10:G59,"✅ Entregue")</f>
-        <v>1</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="14">
-        <f>COUNTIF(G10:G59,"⏳ Pendente")</f>
-        <v>1</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="16">
-        <f>COUNTIF(G10:G59,"🔄 Em revisão")</f>
-        <v>1</v>
-      </c>
-      <c r="L6" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="N6" s="31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="L7" s="23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" s="1"/>
-      <c r="L8" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="N8" s="31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-    </row>
-    <row r="10" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18">
-        <v>1</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="35">
-        <v>46161</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18">
-        <v>2</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="35">
-        <v>46147</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18">
-        <v>3</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18">
-        <v>4</v>
-      </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="18">
-        <v>5</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18">
-        <v>6</v>
-      </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="18">
-        <v>7</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18">
-        <v>8</v>
-      </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="18">
-        <v>9</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="17"/>
-    </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="18">
-        <v>10</v>
-      </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18">
-        <v>11</v>
-      </c>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="18">
-        <v>12</v>
-      </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="18">
-        <v>13</v>
-      </c>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="17"/>
-    </row>
-    <row r="23" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="18">
-        <v>14</v>
-      </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="18">
-        <v>15</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="18">
-        <v>16</v>
-      </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="18">
-        <v>17</v>
-      </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="18">
-        <v>18</v>
-      </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="17"/>
-    </row>
-    <row r="28" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="17"/>
-      <c r="B28" s="18">
-        <v>19</v>
-      </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="17"/>
-    </row>
-    <row r="29" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="18">
-        <v>20</v>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="17"/>
-    </row>
-    <row r="30" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="18">
-        <v>21</v>
-      </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="17"/>
-    </row>
-    <row r="31" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="17"/>
-      <c r="B31" s="18">
-        <v>22</v>
-      </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="17"/>
-    </row>
-    <row r="32" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="17"/>
-      <c r="B32" s="18">
-        <v>23</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="17"/>
-    </row>
-    <row r="33" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="17"/>
-      <c r="B33" s="18">
-        <v>24</v>
-      </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="17"/>
-    </row>
-    <row r="34" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="17"/>
-      <c r="B34" s="18">
-        <v>25</v>
-      </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="17"/>
-    </row>
-    <row r="35" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="17"/>
-      <c r="B35" s="18">
-        <v>26</v>
-      </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="17"/>
-    </row>
-    <row r="36" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="17"/>
-      <c r="B36" s="18">
-        <v>27</v>
-      </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="17"/>
-    </row>
-    <row r="37" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="17"/>
-      <c r="B37" s="18">
-        <v>28</v>
-      </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="17"/>
-    </row>
-    <row r="38" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="17"/>
-      <c r="B38" s="18">
-        <v>29</v>
-      </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="17"/>
-    </row>
-    <row r="39" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="17"/>
-      <c r="B39" s="18">
-        <v>30</v>
-      </c>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="17"/>
-    </row>
-    <row r="41" spans="1:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
-      <c r="B41" s="36"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
-    </row>
-    <row r="42" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="B42:I42"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>